--- a/teacher_forms/003_student_adaptation_to_college_questionnaire--teacher_forms.xlsx
+++ b/teacher_forms/003_student_adaptation_to_college_questionnaire--teacher_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -983,7 +983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -1062,34 +1062,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>school_year_choices</t>
+          <t>adaptation_level_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>high_school</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>High School</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>school_year_choices</t>
+          <t>adaptation_level_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>middle_school</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Middle School</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1135,46 +1135,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>adaptation_level_choices</t>
+          <t>school_program_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>program_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Program 1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>adaptation_level_choices</t>
+          <t>school_program_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>program_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>Program 2</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>program_1</t>
+          <t>program_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Program 1</t>
+          <t>Program 3</t>
         </is>
       </c>
     </row>
@@ -1203,46 +1203,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>program_2</t>
+          <t>program_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Program 2</t>
+          <t>Program 4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>school_program_choices</t>
+          <t>teacher_involvement_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>program_3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Program 3</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>school_program_choices</t>
+          <t>teacher_involvement_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>program_4</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Program 4</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1271,46 +1271,46 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>teacher_involvement_choices</t>
+          <t>student_participation_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>teacher_involvement_choices</t>
+          <t>student_participation_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1356,46 +1356,46 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>student_participation_choices</t>
+          <t>teacher_adaptation_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>student_participation_choices</t>
+          <t>teacher_adaptation_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1441,46 +1441,46 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>teacher_adaptation_choices</t>
+          <t>teacher_adaptation_to_college_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>teacher_adaptation_choices</t>
+          <t>teacher_adaptation_to_college_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1526,44 +1526,10 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>teacher_adaptation_to_college_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>teacher_adaptation_to_college_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>very_high</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
